--- a/Bauteillisten/Bestellliste_DigiKey_V1.xlsx
+++ b/Bauteillisten/Bestellliste_DigiKey_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janne\Desktop\Studium\6. Semester\Active Balancing Projekt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Documents\Uni\Semester 6\Projektarbeit\active-balancing\Bauteillisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54E68740-0B58-48B3-8B0B-74EE237EDA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8C4B6C-0603-47B5-9C8A-78D8C2C717CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -674,20 +674,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="6.77734375" customWidth="1"/>
-    <col min="3" max="3" width="33.77734375" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" customWidth="1"/>
-    <col min="5" max="5" width="43.21875" customWidth="1"/>
-    <col min="6" max="6" width="18.88671875" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="8" width="21.5546875" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="1" max="2" width="6.81640625" customWidth="1"/>
+    <col min="3" max="3" width="33.81640625" customWidth="1"/>
+    <col min="4" max="4" width="29.6328125" customWidth="1"/>
+    <col min="5" max="5" width="43.1796875" customWidth="1"/>
+    <col min="6" max="6" width="18.90625" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -701,7 +701,7 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -733,7 +733,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -762,7 +762,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -791,7 +791,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -820,7 +820,7 @@
         <v>9.4600000000000009</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -849,7 +849,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -878,7 +878,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -907,7 +907,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -936,7 +936,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -965,7 +965,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -994,7 +994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>31.98</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>33.14</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>27</v>
       </c>
